--- a/TASK2/Scenariji/SC05_AutomatskoObavjestavanje.xlsx
+++ b/TASK2/Scenariji/SC05_AutomatskoObavjestavanje.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Automatsko obavjestavanje o isteku clanarine</t>
+          <t>Automatsko obavještavanje o isteku članarine</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Sistem periodicno provjerava clanarine koje isticu i salje email obavjestenja clanovima.</t>
+          <t>Sistem periodično provjerava članarine koje ističu i šalje email obavještenja članovima.</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Asinhrono slanje email obavjestenja o isteku clanarine</t>
+          <t>Asinhrono slanje email obavještenja o isteku članarine</t>
         </is>
       </c>
     </row>
@@ -504,19 +504,19 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - uspjesan zavrsetak</t>
+          <t>Posljedice - uspješan završetak</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Svi clanovi cije clanarine isticu u 7 dana su obavijesteni.</t>
+          <t>Svi clanovi cije članarine ističu u 7 dana su obaviješteni.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - neuspjesan zavrsetak</t>
+          <t>Posljedice - neuspješan završetak</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sistem provjerava clanarine koje isticu i asinhrono salje email obavjestenja.</t>
+          <t>Sistem provjerava članarine koje ističu i asinhrono šalje email obavještenja.</t>
         </is>
       </c>
     </row>
@@ -569,10 +569,11 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Greska pri slanju email-a, Nema clanarina za obavjestavanje</t>
-        </is>
-      </c>
-    </row>
+          <t>Greška pri slanju email-a, Nema članarina za obavještavanje</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -602,56 +603,57 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2. Dohvatanje svih aktivnih clanarina</t>
+          <t>2. Dohvaćanje svih aktivnih članarina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>3. Identifikacija clanarina koje isticu u narednih 7 dana</t>
+          <t>3. Identifikacija članarina koje ističu u narednih 7 dana</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>4. Priprema email obavjestenja za svaku identificiranu clanarinu</t>
+          <t>4. Priprema email obavještenja za svaku identificiranu članarinu</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>5. Asinhrono slanje email obavjestenja</t>
+          <t>5. Asinhrono slanje email obavještenja</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>6. Prijem i dostava email-a clanu</t>
+          <t>6. Prijem i dostava email-a članu</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>7. Evidentiranje slanja obavjestenja</t>
+          <t>7. Evidentiranje slanja obavještenja</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>8. Zavrsavanje ciklusa provjere</t>
-        </is>
-      </c>
-    </row>
+          <t>8. Završavanje ciklusa provjere</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Alternativni Tok - Greska pri slanju email-a</t>
+          <t>Alternativni Tok - Greška pri slanju email-a</t>
         </is>
       </c>
     </row>
@@ -677,21 +679,21 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>6b. Sistem biljezi gresku u log</t>
+          <t>6b. Sistem bilježi grešku u log</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>6c. Sistem oznacava obavjestenje za ponovni pokusaj</t>
+          <t>6c. Sistem oznacava obavještenje za ponovni pokušaj</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>6d. Sistem nastavlja sa sljedecom clanarinom</t>
+          <t>6d. Sistem nastavlja sa sljedećom clanarinom</t>
         </is>
       </c>
     </row>
